--- a/Descargas/Q10/Detalle Cursos/2026-10-16_1448_Detallado_de_cursos_B2G_YES_BOGOTA-2_C1_SEP_2026.xlsx
+++ b/Descargas/Q10/Detalle Cursos/2026-10-16_1448_Detallado_de_cursos_B2G_YES_BOGOTA-2_C1_SEP_2026.xlsx
@@ -1,18 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://centrocolombobogota-my.sharepoint.com/personal/sebastian_mendez_colombobogota_edu_co/Documents/Escritorio/Automatizacion Oxford/Descargas/Q10/Detalle Cursos/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_59DCE7005CA593AC226ED158700D1C3626CF52E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBCC2A2E-8BB4-441E-9BB0-3326FD0AF3BB}"/>
   <bookViews>
-    <workbookView/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2844" uniqueCount="608">
   <si>
     <t>Período</t>
   </si>
@@ -1841,11 +1849,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd/MM/yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1869,32 +1877,32 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1902,73 +1910,530 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DetalladoCursosViewModel_1" displayName="DetalladoCursosViewModel_1" ref="A1:W218">
-  <autoFilter ref="A1:W218"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DetalladoCursosViewModel_1" displayName="DetalladoCursosViewModel_1" ref="A1:W218">
+  <autoFilter ref="A1:W218" xr:uid="{00000000-0009-0000-0100-000001000000}">
+    <filterColumn colId="6">
+      <filters>
+        <filter val="B1.1-5PM100 SDDE_2026-2"/>
+        <filter val="B1.1-5PM101 SDDE_2026-2"/>
+        <filter val="B1.1-5PM102 SDDE_2026-2"/>
+        <filter val="B1.1-5PM103 SDDE_2026-2"/>
+        <filter val="B1.1-5PM104 SDDE_2026-2"/>
+        <filter val="B1.1-5PM87 SDDE_2026-2"/>
+        <filter val="B1.1-5PM88 SDDE_2026-2"/>
+        <filter val="B1.1-5PM89 SDDE_2026-2"/>
+        <filter val="B1.1-5PM90 SDDE_2026-2"/>
+        <filter val="B1.1-5PM91 SDDE_2026-2"/>
+        <filter val="B1.1-5PM92 SDDE_2026-2"/>
+        <filter val="B1.1-5PM93 SDDE_2026-2"/>
+        <filter val="B1.1-5PM94 SDDE_2026-2"/>
+        <filter val="B1.1-5PM95 SDDE_2026-2"/>
+        <filter val="B1.1-5PM96 SDDE_2026-2"/>
+        <filter val="B1.1-5PM97 SDDE_2026-2"/>
+        <filter val="B1.1-5PM98 SDDE_2026-2"/>
+        <filter val="B1.1-5PM99 SDDE_2026-2"/>
+        <filter val="B1.1-7PM147 SDDE_2026-2"/>
+        <filter val="B1.1-7PM148 SDDE_2026-2"/>
+        <filter val="B1.1-7PM149 SDDE_2026-2"/>
+        <filter val="B1.1-7PM150 SDDE_2026-2"/>
+        <filter val="B1.1-7PM151 SDDE_2026-2"/>
+        <filter val="B1.1-7PM152 SDDE_2026-2"/>
+        <filter val="B1.1-7PM153 SDDE_2026-2"/>
+        <filter val="B1.1-7PM154 SDDE_2026-2"/>
+        <filter val="B1.1-7PM155 SDDE_2026-2"/>
+        <filter val="B1.1-7PM156 SDDE_2026-2"/>
+        <filter val="B1.1-7PM157 SDDE_2026-2"/>
+        <filter val="B1.1-7PM158 SDDE_2026-2"/>
+        <filter val="B1.1-7PM159 SDDE_2026-2"/>
+        <filter val="B1.1-7PM160 SDDE_2026-2"/>
+        <filter val="B1.1-7PM161 SDDE_2026-2"/>
+        <filter val="B1.1-7PM162 SDDE_2026-2"/>
+        <filter val="B1.1-7PM163 SDDE_2026-2"/>
+        <filter val="B1.1-7PM164 SDDE_2026-2"/>
+        <filter val="B1.1-7PM165 SDDE_2026-2"/>
+        <filter val="B1.1-7PM166 SDDE_2026-2"/>
+        <filter val="B1.1-7PM167 SDDE_2026-2"/>
+        <filter val="B1.1-7PM168 SDDE_2026-2"/>
+        <filter val="B1.1-7PM169 SDDE_2026-2"/>
+        <filter val="B1.1-7PM170 SDDE_2026-2"/>
+        <filter val="B1.1-7PM171 SDDE_2026-2"/>
+        <filter val="B1.1-7PM172 SDDE_2026-2"/>
+        <filter val="B1.2-5PM105 SDDE_2026-2"/>
+        <filter val="B1.2-5PM106 SDDE_2026-2"/>
+        <filter val="B1.2-5PM107 SDDE_2026-2"/>
+        <filter val="B1.2-5PM108 SDDE_2026-2"/>
+        <filter val="B1.2-5PM109 SDDE_2026-2"/>
+        <filter val="B1.2-5PM110 SDDE_2026-2"/>
+        <filter val="B1.2-5PM111 SDDE_2026-2"/>
+        <filter val="B1.2-5PM112 SDDE_2026-2"/>
+        <filter val="B1.2-5PM113 SDDE_2026-2"/>
+        <filter val="B1.2-5PM114 SDDE_2026-2"/>
+        <filter val="B1.2-5PM115 SDDE_2026-2"/>
+        <filter val="B1.2-5PM116 SDDE_2026-2"/>
+        <filter val="B1.2-5PM117 SDDE_2026-2"/>
+        <filter val="B1.2-5PM118 SDDE_2026-2"/>
+        <filter val="B1.2-5PM119 SDDE_2026-2"/>
+        <filter val="B1.2-5PM120 SDDE_2026-2"/>
+        <filter val="B1.2-5PM121 SDDE_2026-2"/>
+        <filter val="B1.2-5PM122 SDDE_2026-2"/>
+        <filter val="B1.2-5PM123 SDDE_2026-2"/>
+        <filter val="B1.2-5PM124 SDDE_2026-2"/>
+        <filter val="B1.2-5PM125 SDDE_2026-2"/>
+        <filter val="B1.2-5PM126 SDDE_2026-2"/>
+        <filter val="B1.2-5PM127 SDDE_2026-2"/>
+        <filter val="B1.2-5PM128 SDDE_2026-2"/>
+        <filter val="B1.2-5PM129 SDDE_2026-2"/>
+        <filter val="B1.2-5PM130 SDDE_2026-2"/>
+        <filter val="B1.2-5PM131 SDDE_2026-2"/>
+        <filter val="B1.2-5PM132 SDDE_2026-2"/>
+        <filter val="B1.2-5PM133 SDDE_2026-2"/>
+        <filter val="B1.2-5PM134 SDDE_2026-2"/>
+        <filter val="B1.2-5PM135 SDDE_2026-2"/>
+        <filter val="B1.2-5PM136 SDDE_2026-2"/>
+        <filter val="B1.2-7PM173 SDDE_2026-2"/>
+        <filter val="B1.2-7PM174 SDDE_2026-2"/>
+        <filter val="B1.2-7PM175 SDDE_2026-2"/>
+        <filter val="B1.2-7PM176 SDDE_2026-2"/>
+        <filter val="B1.2-7PM177 SDDE_2026-2"/>
+        <filter val="B1.2-7PM178 SDDE_2026-2"/>
+        <filter val="B1.2-7PM179 SDDE_2026-2"/>
+        <filter val="B1.2-7PM180 SDDE_2026-2"/>
+        <filter val="B1.2-7PM181 SDDE_2026-2"/>
+        <filter val="B1.2-7PM182 SDDE_2026-2"/>
+        <filter val="B1.2-7PM183 SDDE_2026-2"/>
+        <filter val="B1.2-7PM184 SDDE_2026-2"/>
+        <filter val="B1.2-7PM185 SDDE_2026-2"/>
+        <filter val="B1.2-7PM186 SDDE_2026-2"/>
+        <filter val="B1.2-7PM187 SDDE_2026-2"/>
+        <filter val="B1.2-7PM188 SDDE_2026-2"/>
+        <filter val="B1.2-7PM189 SDDE_2026-2"/>
+        <filter val="B1.2-7PM190 SDDE_2026-2"/>
+        <filter val="B1.2-7PM191 SDDE_2026-2"/>
+        <filter val="B1.2-7PM192 SDDE_2026-2"/>
+        <filter val="B1.2-7PM193 SDDE_2026-2"/>
+        <filter val="B1.2-7PM194 SDDE_2026-2"/>
+        <filter val="B1.2-7PM195 SDDE_2026-2"/>
+        <filter val="B1.2-7PM196 SDDE_2026-2"/>
+        <filter val="B1.2-7PM197 SDDE_2026-2"/>
+        <filter val="B1.2-7PM198 SDDE_2026-2"/>
+        <filter val="B1.2-7PM199 SDDE_2026-2"/>
+        <filter val="B1.2-7PM200 SDDE_2026-2"/>
+        <filter val="B1.2-7PM201 SDDE_2026-2"/>
+        <filter val="B1.2-7PM202 SDDE_2026-2"/>
+        <filter val="B1.2-7PM203 SDDE_2026-2"/>
+        <filter val="B1.2-7PM204 SDDE_2026-2"/>
+        <filter val="B2.1-5PM137 SDDE_2026-2"/>
+        <filter val="B2.1-5PM138 SDDE_2026-2"/>
+        <filter val="B2.1-5PM139 SDDE_2026-2"/>
+        <filter val="B2.1-5PM140 SDDE_2026-2"/>
+        <filter val="B2.1-5PM141 SDDE_2026-2"/>
+        <filter val="B2.1-5PM142 SDDE_2026-2"/>
+        <filter val="B2.1-5PM143 SDDE_2026-2"/>
+        <filter val="B2.1-5PM144 SDDE_2026-2"/>
+        <filter val="B2.1-5PM145 SDDE_2026-2"/>
+        <filter val="B2.1-5PM146 SDDE_2026-2"/>
+        <filter val="B2.1-7PM205 SDDE_2026-2"/>
+        <filter val="B2.1-7PM206 SDDE_2026-2"/>
+        <filter val="B2.1-7PM207 SDDE_2026-2"/>
+        <filter val="B2.1-7PM208 SDDE_2026-2"/>
+        <filter val="B2.1-7PM209 SDDE_2026-2"/>
+        <filter val="B2.1-7PM210 SDDE_2026-2"/>
+        <filter val="B2.1-7PM211 SDDE_2026-2"/>
+        <filter val="B2.1-7PM212 SDDE_2026-2"/>
+        <filter val="B2.1-7PM213 SDDE_2026-2"/>
+        <filter val="B2.1-7PM214 SDDE_2026-2"/>
+        <filter val="B2.1-7PM215 SDDE_2026-2"/>
+        <filter val="B2.1-7PM216 SDDE_2026-2"/>
+        <filter val="C1.1-7PM217 SDDE_2026-2"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="23">
-    <tableColumn id="1" name="Período"/>
-    <tableColumn id="2" name="Sede - Jornada"/>
-    <tableColumn id="3" name="Programa"/>
-    <tableColumn id="4" name="Modelo evaluación"/>
-    <tableColumn id="5" name="Asignatura"/>
-    <tableColumn id="6" name="Código curso"/>
-    <tableColumn id="7" name="Nombre curso"/>
-    <tableColumn id="8" name="Docente"/>
-    <tableColumn id="9" name="N° matrículados"/>
-    <tableColumn id="10" name="Cupo máximo"/>
-    <tableColumn id="11" name="Fecha inicio"/>
-    <tableColumn id="12" name="Fecha fin"/>
-    <tableColumn id="13" name="Código virtual"/>
-    <tableColumn id="14" name="Días horario"/>
-    <tableColumn id="15" name="Hora inicio horario"/>
-    <tableColumn id="16" name="Hora fin horario"/>
-    <tableColumn id="17" name="Aula horario"/>
-    <tableColumn id="18" name="Horario semanal"/>
-    <tableColumn id="19" name="Intensidad horario"/>
-    <tableColumn id="20" name="Estado"/>
-    <tableColumn id="21" name="Formalizados"/>
-    <tableColumn id="22" name="No formalizados"/>
-    <tableColumn id="23" name="Prematrículados"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Período"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Sede - Jornada"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Programa"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Modelo evaluación"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Asignatura"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Código curso"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Nombre curso"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Docente"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="N° matrículados"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Cupo máximo"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Fecha inicio"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Fecha fin"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Código virtual"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Días horario"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Hora inicio horario"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Hora fin horario"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Aula horario"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Horario semanal"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Intensidad horario"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Estado"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Formalizados"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="No formalizados"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Prematrículados"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W219"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="15.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.5685710906982" customWidth="1" style="1"/>
-    <col min="2" max="2" width="16.4847764968872" customWidth="1" style="1"/>
-    <col min="3" max="3" width="19.3091793060303" customWidth="1" style="1"/>
-    <col min="4" max="4" width="20.3980007171631" customWidth="1" style="1"/>
-    <col min="5" max="5" width="15.7" customWidth="1" style="1"/>
-    <col min="6" max="6" width="21.8023891448975" customWidth="1" style="1"/>
-    <col min="7" max="7" width="25.7084522247314" customWidth="1" style="1"/>
-    <col min="8" max="8" width="34.2756004333496" customWidth="1" style="1"/>
-    <col min="9" max="9" width="17.6930160522461" customWidth="1" style="1"/>
-    <col min="10" max="10" width="15.7553300857544" customWidth="1" style="1"/>
-    <col min="11" max="11" width="15.7" customWidth="1" style="1"/>
-    <col min="12" max="12" width="15.7" customWidth="1" style="1"/>
-    <col min="13" max="13" width="15.828989982605" customWidth="1" style="1"/>
-    <col min="14" max="14" width="37.9003219604492" customWidth="1" style="1"/>
-    <col min="15" max="15" width="20.0163974761963" customWidth="1" style="1"/>
-    <col min="16" max="16" width="17.6347017288208" customWidth="1" style="1"/>
-    <col min="17" max="17" width="15.7" customWidth="1" style="1"/>
-    <col min="18" max="18" width="28.428783416748" customWidth="1" style="1"/>
-    <col min="19" max="19" width="19.8394069671631" customWidth="1" style="1"/>
-    <col min="20" max="20" width="15.7" customWidth="1" style="1"/>
-    <col min="21" max="21" width="15.7" customWidth="1" style="1"/>
-    <col min="22" max="22" width="17.9784517288208" customWidth="1" style="1"/>
-    <col min="23" max="23" width="18.0214204788208" customWidth="1" style="1"/>
-    <col min="24" max="16384" width="15.7" customWidth="1" style="1"/>
+    <col min="1" max="1" width="31.54296875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.453125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.26953125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.36328125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.7265625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="21.81640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="25.7265625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="34.26953125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17.7265625" style="1" customWidth="1"/>
+    <col min="10" max="12" width="15.7265625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="15.81640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="37.90625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="20" style="1" customWidth="1"/>
+    <col min="16" max="16" width="17.6328125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="15.7265625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="28.453125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="19.81640625" style="1" customWidth="1"/>
+    <col min="20" max="21" width="15.7265625" style="1" customWidth="1"/>
+    <col min="22" max="23" width="18" style="1" customWidth="1"/>
+    <col min="24" max="24" width="15.7265625" style="1" customWidth="1"/>
+    <col min="25" max="16384" width="15.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2039,7 +2504,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>23</v>
       </c>
@@ -2106,7 +2571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>23</v>
       </c>
@@ -2173,7 +2638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>23</v>
       </c>
@@ -2240,7 +2705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>23</v>
       </c>
@@ -2307,7 +2772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>23</v>
       </c>
@@ -2374,7 +2839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
         <v>23</v>
       </c>
@@ -2441,7 +2906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>23</v>
       </c>
@@ -2508,7 +2973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>23</v>
       </c>
@@ -2575,7 +3040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>23</v>
       </c>
@@ -2642,7 +3107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
         <v>23</v>
       </c>
@@ -2709,7 +3174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>23</v>
       </c>
@@ -2776,7 +3241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>23</v>
       </c>
@@ -2843,7 +3308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>23</v>
       </c>
@@ -2910,7 +3375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
         <v>23</v>
       </c>
@@ -2977,7 +3442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
         <v>23</v>
       </c>
@@ -3044,7 +3509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
         <v>23</v>
       </c>
@@ -3111,7 +3576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>23</v>
       </c>
@@ -3178,7 +3643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
         <v>23</v>
       </c>
@@ -3245,7 +3710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
         <v>23</v>
       </c>
@@ -3312,7 +3777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
         <v>23</v>
       </c>
@@ -3379,7 +3844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
         <v>23</v>
       </c>
@@ -3446,7 +3911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
         <v>23</v>
       </c>
@@ -3513,7 +3978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
         <v>23</v>
       </c>
@@ -3580,7 +4045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A25" s="6" t="s">
         <v>23</v>
       </c>
@@ -3647,7 +4112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
         <v>23</v>
       </c>
@@ -3714,7 +4179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
         <v>23</v>
       </c>
@@ -3781,7 +4246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
         <v>23</v>
       </c>
@@ -3848,7 +4313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
         <v>23</v>
       </c>
@@ -3915,7 +4380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A30" s="6" t="s">
         <v>23</v>
       </c>
@@ -3982,7 +4447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A31" s="6" t="s">
         <v>23</v>
       </c>
@@ -4049,7 +4514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A32" s="6" t="s">
         <v>23</v>
       </c>
@@ -4116,7 +4581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="6" t="s">
         <v>23</v>
       </c>
@@ -4183,7 +4648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
         <v>23</v>
       </c>
@@ -4250,7 +4715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
         <v>23</v>
       </c>
@@ -4317,7 +4782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
         <v>23</v>
       </c>
@@ -4384,7 +4849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="6" t="s">
         <v>23</v>
       </c>
@@ -4451,7 +4916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
         <v>23</v>
       </c>
@@ -4518,7 +4983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A39" s="6" t="s">
         <v>23</v>
       </c>
@@ -4585,7 +5050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A40" s="6" t="s">
         <v>23</v>
       </c>
@@ -4652,7 +5117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A41" s="6" t="s">
         <v>23</v>
       </c>
@@ -4719,7 +5184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A42" s="6" t="s">
         <v>23</v>
       </c>
@@ -4786,7 +5251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A43" s="6" t="s">
         <v>23</v>
       </c>
@@ -4853,7 +5318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A44" s="6" t="s">
         <v>23</v>
       </c>
@@ -4920,7 +5385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A45" s="6" t="s">
         <v>23</v>
       </c>
@@ -4987,7 +5452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="6" t="s">
         <v>23</v>
       </c>
@@ -5054,7 +5519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A47" s="6" t="s">
         <v>23</v>
       </c>
@@ -5121,7 +5586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="6" t="s">
         <v>23</v>
       </c>
@@ -5188,7 +5653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A49" s="6" t="s">
         <v>23</v>
       </c>
@@ -5255,7 +5720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A50" s="6" t="s">
         <v>23</v>
       </c>
@@ -5322,7 +5787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A51" s="6" t="s">
         <v>23</v>
       </c>
@@ -5389,7 +5854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A52" s="6" t="s">
         <v>23</v>
       </c>
@@ -5456,7 +5921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="6" t="s">
         <v>23</v>
       </c>
@@ -5523,7 +5988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A54" s="6" t="s">
         <v>23</v>
       </c>
@@ -5590,7 +6055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A55" s="6" t="s">
         <v>23</v>
       </c>
@@ -5657,7 +6122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="6" t="s">
         <v>23</v>
       </c>
@@ -5724,7 +6189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A57" s="6" t="s">
         <v>23</v>
       </c>
@@ -5791,7 +6256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A58" s="6" t="s">
         <v>23</v>
       </c>
@@ -5858,7 +6323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A59" s="6" t="s">
         <v>23</v>
       </c>
@@ -5925,7 +6390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A60" s="6" t="s">
         <v>23</v>
       </c>
@@ -5992,7 +6457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A61" s="6" t="s">
         <v>23</v>
       </c>
@@ -6059,7 +6524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A62" s="6" t="s">
         <v>23</v>
       </c>
@@ -6126,7 +6591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A63" s="6" t="s">
         <v>23</v>
       </c>
@@ -6193,7 +6658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="6" t="s">
         <v>23</v>
       </c>
@@ -6260,7 +6725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A65" s="6" t="s">
         <v>23</v>
       </c>
@@ -6327,7 +6792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A66" s="6" t="s">
         <v>23</v>
       </c>
@@ -6394,7 +6859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" s="6" t="s">
         <v>23</v>
       </c>
@@ -6461,7 +6926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A68" s="6" t="s">
         <v>23</v>
       </c>
@@ -6528,7 +6993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" s="6" t="s">
         <v>23</v>
       </c>
@@ -6595,7 +7060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" s="6" t="s">
         <v>23</v>
       </c>
@@ -6662,7 +7127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" s="6" t="s">
         <v>23</v>
       </c>
@@ -6729,7 +7194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A72" s="6" t="s">
         <v>23</v>
       </c>
@@ -6796,7 +7261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" s="6" t="s">
         <v>23</v>
       </c>
@@ -6863,7 +7328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" s="6" t="s">
         <v>23</v>
       </c>
@@ -6930,7 +7395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" s="6" t="s">
         <v>23</v>
       </c>
@@ -6997,7 +7462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" s="6" t="s">
         <v>23</v>
       </c>
@@ -7064,7 +7529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A77" s="6" t="s">
         <v>23</v>
       </c>
@@ -7131,7 +7596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A78" s="6" t="s">
         <v>23</v>
       </c>
@@ -7198,7 +7663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="6" t="s">
         <v>23</v>
       </c>
@@ -7265,7 +7730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="6" t="s">
         <v>23</v>
       </c>
@@ -7332,7 +7797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="6" t="s">
         <v>23</v>
       </c>
@@ -7399,7 +7864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" s="6" t="s">
         <v>23</v>
       </c>
@@ -7466,7 +7931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="6" t="s">
         <v>23</v>
       </c>
@@ -7533,7 +7998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" s="6" t="s">
         <v>23</v>
       </c>
@@ -7600,7 +8065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A85" s="6" t="s">
         <v>23</v>
       </c>
@@ -7667,7 +8132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A86" s="6" t="s">
         <v>23</v>
       </c>
@@ -7734,7 +8199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" s="6" t="s">
         <v>23</v>
       </c>
@@ -7801,7 +8266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" s="6" t="s">
         <v>23</v>
       </c>
@@ -7868,7 +8333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" s="6" t="s">
         <v>23</v>
       </c>
@@ -7935,7 +8400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" s="6" t="s">
         <v>23</v>
       </c>
@@ -8002,7 +8467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" s="6" t="s">
         <v>23</v>
       </c>
@@ -8069,7 +8534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A92" s="6" t="s">
         <v>23</v>
       </c>
@@ -8136,7 +8601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A93" s="6" t="s">
         <v>23</v>
       </c>
@@ -8203,7 +8668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" s="6" t="s">
         <v>23</v>
       </c>
@@ -8270,7 +8735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" s="6" t="s">
         <v>23</v>
       </c>
@@ -8337,7 +8802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A96" s="6" t="s">
         <v>23</v>
       </c>
@@ -8404,7 +8869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A97" s="6" t="s">
         <v>23</v>
       </c>
@@ -8471,7 +8936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" s="6" t="s">
         <v>23</v>
       </c>
@@ -8538,7 +9003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" s="6" t="s">
         <v>23</v>
       </c>
@@ -8605,7 +9070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" s="6" t="s">
         <v>23</v>
       </c>
@@ -8672,7 +9137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" s="6" t="s">
         <v>23</v>
       </c>
@@ -8739,7 +9204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" s="6" t="s">
         <v>23</v>
       </c>
@@ -8806,7 +9271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A103" s="6" t="s">
         <v>23</v>
       </c>
@@ -8873,7 +9338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" s="6" t="s">
         <v>23</v>
       </c>
@@ -8940,7 +9405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" s="6" t="s">
         <v>23</v>
       </c>
@@ -9007,7 +9472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A106" s="6" t="s">
         <v>23</v>
       </c>
@@ -9074,7 +9539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" s="6" t="s">
         <v>23</v>
       </c>
@@ -9141,7 +9606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" s="6" t="s">
         <v>23</v>
       </c>
@@ -9208,7 +9673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" s="6" t="s">
         <v>23</v>
       </c>
@@ -9275,7 +9740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A110" s="6" t="s">
         <v>23</v>
       </c>
@@ -9342,7 +9807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A111" s="6" t="s">
         <v>23</v>
       </c>
@@ -9409,7 +9874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" s="6" t="s">
         <v>23</v>
       </c>
@@ -9476,7 +9941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A113" s="6" t="s">
         <v>23</v>
       </c>
@@ -9543,7 +10008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" s="6" t="s">
         <v>23</v>
       </c>
@@ -9610,7 +10075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A115" s="6" t="s">
         <v>23</v>
       </c>
@@ -9677,7 +10142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A116" s="6" t="s">
         <v>23</v>
       </c>
@@ -9744,7 +10209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A117" s="6" t="s">
         <v>23</v>
       </c>
@@ -9811,7 +10276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A118" s="6" t="s">
         <v>23</v>
       </c>
@@ -9878,7 +10343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" s="6" t="s">
         <v>23</v>
       </c>
@@ -9945,7 +10410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A120" s="6" t="s">
         <v>23</v>
       </c>
@@ -10012,7 +10477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A121" s="6" t="s">
         <v>23</v>
       </c>
@@ -10079,7 +10544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A122" s="6" t="s">
         <v>23</v>
       </c>
@@ -10146,7 +10611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A123" s="6" t="s">
         <v>23</v>
       </c>
@@ -10213,7 +10678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" s="6" t="s">
         <v>23</v>
       </c>
@@ -10280,7 +10745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" s="6" t="s">
         <v>23</v>
       </c>
@@ -10347,7 +10812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A126" s="6" t="s">
         <v>23</v>
       </c>
@@ -10414,7 +10879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A127" s="6" t="s">
         <v>23</v>
       </c>
@@ -10481,7 +10946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A128" s="6" t="s">
         <v>23</v>
       </c>
@@ -10548,7 +11013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" s="6" t="s">
         <v>23</v>
       </c>
@@ -10615,7 +11080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" s="6" t="s">
         <v>23</v>
       </c>
@@ -10682,7 +11147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A131" s="6" t="s">
         <v>23</v>
       </c>
@@ -10749,7 +11214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A132" s="6" t="s">
         <v>23</v>
       </c>
@@ -10816,7 +11281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A133" s="6" t="s">
         <v>23</v>
       </c>
@@ -10883,7 +11348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A134" s="6" t="s">
         <v>23</v>
       </c>
@@ -10950,7 +11415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" s="6" t="s">
         <v>23</v>
       </c>
@@ -11017,7 +11482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A136" s="6" t="s">
         <v>23</v>
       </c>
@@ -11084,7 +11549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A137" s="6" t="s">
         <v>23</v>
       </c>
@@ -11151,7 +11616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A138" s="6" t="s">
         <v>23</v>
       </c>
@@ -11218,7 +11683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A139" s="6" t="s">
         <v>23</v>
       </c>
@@ -11285,7 +11750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A140" s="6" t="s">
         <v>23</v>
       </c>
@@ -11352,7 +11817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" s="6" t="s">
         <v>23</v>
       </c>
@@ -11419,7 +11884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A142" s="6" t="s">
         <v>23</v>
       </c>
@@ -11486,7 +11951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A143" s="6" t="s">
         <v>23</v>
       </c>
@@ -11553,7 +12018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A144" s="6" t="s">
         <v>23</v>
       </c>
@@ -11620,7 +12085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A145" s="6" t="s">
         <v>23</v>
       </c>
@@ -11687,7 +12152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A146" s="6" t="s">
         <v>23</v>
       </c>
@@ -11754,7 +12219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" s="6" t="s">
         <v>23</v>
       </c>
@@ -11821,7 +12286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" s="6" t="s">
         <v>23</v>
       </c>
@@ -11888,7 +12353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A149" s="6" t="s">
         <v>23</v>
       </c>
@@ -11955,7 +12420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A150" s="6" t="s">
         <v>23</v>
       </c>
@@ -12022,7 +12487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A151" s="6" t="s">
         <v>23</v>
       </c>
@@ -12089,7 +12554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A152" s="6" t="s">
         <v>23</v>
       </c>
@@ -12156,7 +12621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A153" s="6" t="s">
         <v>23</v>
       </c>
@@ -12223,7 +12688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A154" s="6" t="s">
         <v>23</v>
       </c>
@@ -12290,7 +12755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A155" s="6" t="s">
         <v>23</v>
       </c>
@@ -12357,7 +12822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A156" s="6" t="s">
         <v>23</v>
       </c>
@@ -12424,7 +12889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A157" s="6" t="s">
         <v>23</v>
       </c>
@@ -12491,7 +12956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" s="6" t="s">
         <v>23</v>
       </c>
@@ -12558,7 +13023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A159" s="6" t="s">
         <v>23</v>
       </c>
@@ -12625,7 +13090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A160" s="6" t="s">
         <v>23</v>
       </c>
@@ -12692,7 +13157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A161" s="6" t="s">
         <v>23</v>
       </c>
@@ -12759,7 +13224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A162" s="6" t="s">
         <v>23</v>
       </c>
@@ -12826,7 +13291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A163" s="6" t="s">
         <v>23</v>
       </c>
@@ -12893,7 +13358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A164" s="6" t="s">
         <v>23</v>
       </c>
@@ -12960,7 +13425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A165" s="6" t="s">
         <v>23</v>
       </c>
@@ -13027,7 +13492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" s="6" t="s">
         <v>23</v>
       </c>
@@ -13094,7 +13559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" s="6" t="s">
         <v>23</v>
       </c>
@@ -13161,7 +13626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A168" s="6" t="s">
         <v>23</v>
       </c>
@@ -13228,7 +13693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A169" s="6" t="s">
         <v>23</v>
       </c>
@@ -13295,7 +13760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A170" s="6" t="s">
         <v>23</v>
       </c>
@@ -13362,7 +13827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A171" s="6" t="s">
         <v>23</v>
       </c>
@@ -13429,7 +13894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A172" s="6" t="s">
         <v>23</v>
       </c>
@@ -13496,7 +13961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A173" s="6" t="s">
         <v>23</v>
       </c>
@@ -13563,7 +14028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" s="6" t="s">
         <v>23</v>
       </c>
@@ -13630,7 +14095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A175" s="6" t="s">
         <v>23</v>
       </c>
@@ -13697,7 +14162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" s="6" t="s">
         <v>23</v>
       </c>
@@ -13764,7 +14229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" s="6" t="s">
         <v>23</v>
       </c>
@@ -13831,7 +14296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A178" s="6" t="s">
         <v>23</v>
       </c>
@@ -13898,7 +14363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A179" s="6" t="s">
         <v>23</v>
       </c>
@@ -13965,7 +14430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A180" s="6" t="s">
         <v>23</v>
       </c>
@@ -14032,7 +14497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" s="6" t="s">
         <v>23</v>
       </c>
@@ -14099,7 +14564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A182" s="6" t="s">
         <v>23</v>
       </c>
@@ -14166,7 +14631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A183" s="6" t="s">
         <v>23</v>
       </c>
@@ -14233,7 +14698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" s="6" t="s">
         <v>23</v>
       </c>
@@ -14300,7 +14765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" s="6" t="s">
         <v>23</v>
       </c>
@@ -14367,7 +14832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" s="6" t="s">
         <v>23</v>
       </c>
@@ -14434,7 +14899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A187" s="6" t="s">
         <v>23</v>
       </c>
@@ -14501,7 +14966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" s="6" t="s">
         <v>23</v>
       </c>
@@ -14568,7 +15033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A189" s="6" t="s">
         <v>23</v>
       </c>
@@ -14635,7 +15100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A190" s="6" t="s">
         <v>23</v>
       </c>
@@ -14702,7 +15167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" s="6" t="s">
         <v>23</v>
       </c>
@@ -14769,7 +15234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192">
+    <row r="192" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A192" s="6" t="s">
         <v>23</v>
       </c>
@@ -14836,7 +15301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193">
+    <row r="193" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A193" s="6" t="s">
         <v>23</v>
       </c>
@@ -14903,7 +15368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194">
+    <row r="194" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A194" s="6" t="s">
         <v>23</v>
       </c>
@@ -14970,7 +15435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195">
+    <row r="195" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" s="6" t="s">
         <v>23</v>
       </c>
@@ -15037,7 +15502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" s="6" t="s">
         <v>23</v>
       </c>
@@ -15104,7 +15569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197">
+    <row r="197" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A197" s="6" t="s">
         <v>23</v>
       </c>
@@ -15171,7 +15636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198">
+    <row r="198" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A198" s="6" t="s">
         <v>23</v>
       </c>
@@ -15238,7 +15703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199">
+    <row r="199" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A199" s="6" t="s">
         <v>23</v>
       </c>
@@ -15305,7 +15770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200">
+    <row r="200" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A200" s="6" t="s">
         <v>23</v>
       </c>
@@ -15372,7 +15837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201">
+    <row r="201" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A201" s="6" t="s">
         <v>23</v>
       </c>
@@ -15439,7 +15904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202">
+    <row r="202" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A202" s="6" t="s">
         <v>23</v>
       </c>
@@ -15506,7 +15971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203">
+    <row r="203" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A203" s="6" t="s">
         <v>23</v>
       </c>
@@ -15573,7 +16038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204">
+    <row r="204" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" s="6" t="s">
         <v>23</v>
       </c>
@@ -15640,7 +16105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205">
+    <row r="205" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" s="6" t="s">
         <v>23</v>
       </c>
@@ -15707,7 +16172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206">
+    <row r="206" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A206" s="6" t="s">
         <v>23</v>
       </c>
@@ -15774,7 +16239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207">
+    <row r="207" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A207" s="6" t="s">
         <v>23</v>
       </c>
@@ -15841,7 +16306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208">
+    <row r="208" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" s="6" t="s">
         <v>23</v>
       </c>
@@ -15908,7 +16373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209">
+    <row r="209" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" s="6" t="s">
         <v>23</v>
       </c>
@@ -15975,7 +16440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210">
+    <row r="210" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" s="6" t="s">
         <v>23</v>
       </c>
@@ -16042,7 +16507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211">
+    <row r="211" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A211" s="6" t="s">
         <v>23</v>
       </c>
@@ -16109,7 +16574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212">
+    <row r="212" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" s="6" t="s">
         <v>23</v>
       </c>
@@ -16176,7 +16641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213">
+    <row r="213" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A213" s="6" t="s">
         <v>23</v>
       </c>
@@ -16243,7 +16708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214">
+    <row r="214" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A214" s="6" t="s">
         <v>23</v>
       </c>
@@ -16310,7 +16775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215">
+    <row r="215" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" s="6" t="s">
         <v>23</v>
       </c>
@@ -16377,7 +16842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216">
+    <row r="216" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A216" s="6" t="s">
         <v>23</v>
       </c>
@@ -16444,7 +16909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217">
+    <row r="217" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A217" s="6" t="s">
         <v>23</v>
       </c>
@@ -16511,7 +16976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218">
+    <row r="218" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A218" s="6" t="s">
         <v>23</v>
       </c>
@@ -16578,7 +17043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219">
+    <row r="219" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
@@ -16604,8 +17069,8 @@
       <c r="W219" s="3"/>
     </row>
   </sheetData>
-  <headerFooter/>
-  <tableParts>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
